--- a/Result/profitability/8163.xlsx
+++ b/Result/profitability/8163.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.36375</v>
+        <v>0.3175</v>
       </c>
       <c r="N2" t="n">
-        <v>16.5325</v>
+        <v>16.33625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.34875</v>
+        <v>0.33625</v>
       </c>
       <c r="N3" t="n">
-        <v>15.7025</v>
+        <v>15.56</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.03</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42625</v>
+        <v>0.43875</v>
       </c>
       <c r="N4" t="n">
-        <v>15.17625</v>
+        <v>15.0175</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3875</v>
+        <v>0.39875</v>
       </c>
       <c r="N5" t="n">
-        <v>14.0125</v>
+        <v>14.0725</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>0.39</v>
+        <v>0.425</v>
       </c>
       <c r="N6" t="n">
-        <v>13.25625</v>
+        <v>13.56125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.44875</v>
+        <v>0.48125</v>
       </c>
       <c r="N7" t="n">
-        <v>12.8325</v>
+        <v>12.94875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5775</v>
+        <v>0.5912500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>12.52125</v>
+        <v>12.345</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="N9" t="n">
         <v>11.86125</v>
@@ -2026,7 +2026,7 @@
         <v>0.03</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5750000000000001</v>
+        <v>0.575</v>
       </c>
       <c r="N13" t="n">
         <v>11.645</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8163</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7517</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6271</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1246</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="G75" t="n">
+        <v>148</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-44</v>
+      </c>
+      <c r="J75" t="n">
+        <v>105</v>
+      </c>
+      <c r="K75" t="n">
+        <v>86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.26375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.7725</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5499999999999998</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07837687604224575</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4090909090909092</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.4799999999999969</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02981366459627299</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
